--- a/skillsheet/template.xlsx
+++ b/skillsheet/template.xlsx
@@ -3730,7 +3730,7 @@
       <c r="T5" s="251" t="n"/>
       <c r="U5" s="132" t="inlineStr">
         <is>
-          <t>https://jp.a-kusama.com</t>
+          <t>https://www.a-kusama.com/</t>
         </is>
       </c>
       <c r="V5" s="251" t="n"/>
